--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:57:51+00:00</t>
+    <t>2026-08-31T21:27:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10470" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10783" uniqueCount="579">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:27:57+00:00</t>
+    <t>2026-08-31T22:12:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1715,6 +1715,65 @@
   </si>
   <si>
     <t>Finanzierung der Studie</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn</t>
+  </si>
+  <si>
+    <t>Person, die an einer Studie teilnimmt (unter Umständen, während sie Patient:in in einer Gesundheitseinrichtung ist)</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.id</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.SubjektIdentifizierungscode</t>
+  </si>
+  <si>
+    <t>Eindeutiger Identifikator eines Patienten im Kontext eines Forschungsprojekts (klinische Studie, Use Case)</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.Rechtsgrundlage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Consent)
+</t>
+  </si>
+  <si>
+    <t>Rechtsgrundlage (z.B. Einwilligung) aufgrund die PatientIn in die Studie eingeschlossen werden darf.</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.BeginnTeilnahme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Beginn der Teilnahme der Person an der Studie.</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.EndeTeilnahme</t>
+  </si>
+  <si>
+    <t>Ende der Teilnahme der Person an der Studie.</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.StatusDerTeilnahme</t>
+  </si>
+  <si>
+    <t>Stand der Teilnahme einer Person an der Studie, z.B. eingeschlossen, widerrufen, abgeschlossen etc.</t>
+  </si>
+  <si>
+    <t>mii-lm-studie-logicalmodel.ProbandIn.BezeichnungDerStudie</t>
+  </si>
+  <si>
+    <t>Identifikator der Studie</t>
   </si>
 </sst>
 </file>
@@ -2016,7 +2075,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ332"/>
+  <dimension ref="A1:AJ342"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="76.98828125" customWidth="true" bestFit="true"/>
@@ -2029,7 +2088,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="16.59375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -35538,6 +35597,1012 @@
         <v>73</v>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B333" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C333" s="2"/>
+      <c r="D333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E333" s="2"/>
+      <c r="F333" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G333" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K333" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L333" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M333" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N333" s="2"/>
+      <c r="O333" s="2"/>
+      <c r="P333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q333" s="2"/>
+      <c r="R333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF333" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AG333" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH333" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI333" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ333" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B334" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C334" s="2"/>
+      <c r="D334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E334" s="2"/>
+      <c r="F334" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G334" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K334" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L334" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M334" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N334" s="2"/>
+      <c r="O334" s="2"/>
+      <c r="P334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q334" s="2"/>
+      <c r="R334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF334" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AG334" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH334" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI334" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ334" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B335" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C335" s="2"/>
+      <c r="D335" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E335" s="2"/>
+      <c r="F335" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G335" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K335" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L335" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M335" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="N335" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O335" s="2"/>
+      <c r="P335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q335" s="2"/>
+      <c r="R335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB335" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC335" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE335" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF335" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG335" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH335" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI335" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ335" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B336" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C336" s="2"/>
+      <c r="D336" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E336" s="2"/>
+      <c r="F336" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G336" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I336" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="J336" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K336" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L336" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M336" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N336" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O336" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q336" s="2"/>
+      <c r="R336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF336" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG336" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH336" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI336" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ336" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B337" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C337" s="2"/>
+      <c r="D337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E337" s="2"/>
+      <c r="F337" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G337" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K337" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L337" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M337" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N337" s="2"/>
+      <c r="O337" s="2"/>
+      <c r="P337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q337" s="2"/>
+      <c r="R337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF337" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG337" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH337" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI337" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ337" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B338" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C338" s="2"/>
+      <c r="D338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E338" s="2"/>
+      <c r="F338" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G338" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K338" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L338" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M338" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N338" s="2"/>
+      <c r="O338" s="2"/>
+      <c r="P338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q338" s="2"/>
+      <c r="R338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF338" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG338" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH338" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI338" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ338" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B339" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C339" s="2"/>
+      <c r="D339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E339" s="2"/>
+      <c r="F339" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G339" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K339" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L339" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M339" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N339" s="2"/>
+      <c r="O339" s="2"/>
+      <c r="P339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q339" s="2"/>
+      <c r="R339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF339" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG339" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH339" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI339" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ339" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B340" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C340" s="2"/>
+      <c r="D340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E340" s="2"/>
+      <c r="F340" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G340" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K340" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L340" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M340" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N340" s="2"/>
+      <c r="O340" s="2"/>
+      <c r="P340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q340" s="2"/>
+      <c r="R340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF340" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AG340" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH340" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI340" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ340" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B341" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C341" s="2"/>
+      <c r="D341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E341" s="2"/>
+      <c r="F341" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G341" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K341" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L341" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M341" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N341" s="2"/>
+      <c r="O341" s="2"/>
+      <c r="P341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q341" s="2"/>
+      <c r="R341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF341" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG341" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH341" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI341" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ341" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B342" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C342" s="2"/>
+      <c r="D342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E342" s="2"/>
+      <c r="F342" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G342" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K342" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L342" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M342" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N342" s="2"/>
+      <c r="O342" s="2"/>
+      <c r="P342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q342" s="2"/>
+      <c r="R342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF342" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG342" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH342" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI342" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ342" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T22:12:16+00:00</t>
+    <t>2026-08-31T22:17:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-mii-lm-studie-logicalmodel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T22:17:14+00:00</t>
+    <t>2026-09-01T10:01:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
